--- a/public/exports/65120119.xlsx
+++ b/public/exports/65120119.xlsx
@@ -131,7 +131,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118905</t>
+          <t xml:space="preserve">2121205</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -140,7 +140,7 @@
         </is>
       </c>
       <c r="F3">
-        <v>257</v>
+        <v>624</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -181,16 +181,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120299</t>
+          <t xml:space="preserve">2121754</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F4">
-        <v>858</v>
+        <v>339</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120620</t>
+          <t xml:space="preserve">226330, 226331, 226332</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F5">
-        <v>698</v>
+        <v>784</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121205</t>
+          <t xml:space="preserve">226855, 226856</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F6">
-        <v>624</v>
+        <v>1125</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121754</t>
+          <t xml:space="preserve">227307, 227308, 227309, 227310, 227311, 227312</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F7">
-        <v>339</v>
+        <v>584</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">712017, 2120435</t>
+          <t xml:space="preserve">228152, 228153</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F8">
-        <v>254</v>
+        <v>1744</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2117657</t>
+          <t xml:space="preserve">229532, 229533, 229534</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -440,21 +440,21 @@
         </is>
       </c>
       <c r="F9">
-        <v>457</v>
+        <v>9132</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011133</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-03</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119016</t>
+          <t xml:space="preserve">2117657</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -490,16 +490,16 @@
         </is>
       </c>
       <c r="F10">
-        <v>338</v>
+        <v>457</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018781</t>
+          <t xml:space="preserve">200011133</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-17</t>
+          <t xml:space="preserve">2019-03-03</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118940</t>
+          <t xml:space="preserve">2119016</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="F11">
-        <v>1098</v>
+        <v>338</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020473</t>
+          <t xml:space="preserve">200018781</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-08-17</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">7910620</t>
+          <t xml:space="preserve">2118940</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -590,16 +590,16 @@
         </is>
       </c>
       <c r="F12">
-        <v>1418</v>
+        <v>1098</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">311037217</t>
+          <t xml:space="preserve">200020473</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-02-07</t>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -631,35 +631,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302727</t>
+          <t xml:space="preserve">2118905</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F13">
-        <v>1991</v>
+        <v>257</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266310</t>
+          <t xml:space="preserve">200020916</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-15</t>
+          <t xml:space="preserve">2019-09-22</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -681,35 +681,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121204</t>
+          <t xml:space="preserve">7910620</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F14">
-        <v>2582</v>
+        <v>1418</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">311316443</t>
+          <t xml:space="preserve">311037217</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-25</t>
+          <t xml:space="preserve">2024-02-07</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -731,25 +731,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121011</t>
+          <t xml:space="preserve">1302727</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F15">
-        <v>721</v>
+        <v>1991</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311353004</t>
+          <t xml:space="preserve">311266310</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-23</t>
+          <t xml:space="preserve">2027-08-15</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -781,25 +781,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118050</t>
+          <t xml:space="preserve">2121204</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F16">
-        <v>485</v>
+        <v>2582</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548536</t>
+          <t xml:space="preserve">311316443</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-16</t>
+          <t xml:space="preserve">2028-05-25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -831,25 +831,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119099</t>
+          <t xml:space="preserve">2121011</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F17">
-        <v>370</v>
+        <v>721</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556179</t>
+          <t xml:space="preserve">311353004</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-19</t>
+          <t xml:space="preserve">2028-12-23</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -881,25 +881,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119099</t>
+          <t xml:space="preserve">2118050</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F18">
-        <v>370</v>
+        <v>485</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556179</t>
+          <t xml:space="preserve">311548536</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-19</t>
+          <t xml:space="preserve">2031-09-16</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -931,25 +931,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119099</t>
+          <t xml:space="preserve">2120377</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F19">
-        <v>370</v>
+        <v>1498</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556179</t>
+          <t xml:space="preserve">311586001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-19</t>
+          <t xml:space="preserve">2031-12-07</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -986,20 +986,20 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F20">
-        <v>1140</v>
+        <v>370</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556179</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-19</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1036,20 +1036,20 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F21">
-        <v>1394</v>
+        <v>370</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556179</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-19</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1086,20 +1086,20 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F22">
-        <v>499</v>
+        <v>370</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556179</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-19</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1136,20 +1136,20 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F23">
-        <v>409</v>
+        <v>1140</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556179</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-19</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1186,20 +1186,20 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F24">
-        <v>356</v>
+        <v>1394</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556179</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-19</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1236,20 +1236,20 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F25">
-        <v>2026</v>
+        <v>499</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556179</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-19</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1286,20 +1286,20 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F26">
-        <v>1968</v>
+        <v>409</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556179</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-19</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1336,20 +1336,20 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F27">
-        <v>1175</v>
+        <v>356</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556179</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-19</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1386,20 +1386,20 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F28">
-        <v>997</v>
+        <v>2026</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556179</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-19</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1431,25 +1431,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120377</t>
+          <t xml:space="preserve">2119099</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F29">
-        <v>1498</v>
+        <v>1968</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586001</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1476,30 +1476,30 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">157</t>
+          <t xml:space="preserve">161</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018964</t>
+          <t xml:space="preserve">2119099</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F30">
-        <v>321</v>
+        <v>1175</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588707</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1531,25 +1531,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2117851</t>
+          <t xml:space="preserve">2119099</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F31">
-        <v>1941</v>
+        <v>997</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588724</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">161</t>
+          <t xml:space="preserve">157</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119886</t>
+          <t xml:space="preserve">2018964</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1590,11 +1590,11 @@
         </is>
       </c>
       <c r="F32">
-        <v>410</v>
+        <v>321</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588725</t>
+          <t xml:space="preserve">311588707</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1631,20 +1631,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119886</t>
+          <t xml:space="preserve">2117851</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F33">
-        <v>472</v>
+        <v>1941</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588725</t>
+          <t xml:space="preserve">311588724</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1686,11 +1686,11 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F34">
-        <v>1892</v>
+        <v>410</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1736,11 +1736,11 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F35">
-        <v>1678</v>
+        <v>472</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1786,11 +1786,11 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F36">
-        <v>3639</v>
+        <v>1892</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1836,11 +1836,11 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F37">
-        <v>499</v>
+        <v>1678</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,25 +1881,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">100040948</t>
+          <t xml:space="preserve">2119886</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F38">
-        <v>1186</v>
+        <v>3639</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590092</t>
+          <t xml:space="preserve">311588725</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2117855</t>
+          <t xml:space="preserve">2119886</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F39">
-        <v>567</v>
+        <v>499</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590100</t>
+          <t xml:space="preserve">311588725</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1981,20 +1981,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2117855</t>
+          <t xml:space="preserve">100040948</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F40">
-        <v>591</v>
+        <v>1186</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590100</t>
+          <t xml:space="preserve">311590092</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118958</t>
+          <t xml:space="preserve">2117855</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2040,11 +2040,11 @@
         </is>
       </c>
       <c r="F41">
-        <v>4333</v>
+        <v>567</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590123</t>
+          <t xml:space="preserve">311590100</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2081,20 +2081,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118958</t>
+          <t xml:space="preserve">2117855</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F42">
-        <v>386</v>
+        <v>591</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590111</t>
+          <t xml:space="preserve">311590100</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2136,15 +2136,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F43">
-        <v>1122</v>
+        <v>4333</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590120</t>
+          <t xml:space="preserve">311590114</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2186,15 +2186,15 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F44">
-        <v>2621</v>
+        <v>386</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590120</t>
+          <t xml:space="preserve">311590111</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2231,20 +2231,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119589</t>
+          <t xml:space="preserve">2118958</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F45">
-        <v>667</v>
+        <v>1122</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590105</t>
+          <t xml:space="preserve">311590114</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2281,25 +2281,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">7942754</t>
+          <t xml:space="preserve">2118958</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F46">
-        <v>1323</v>
+        <v>2621</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590434</t>
+          <t xml:space="preserve">311590114</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-04</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">7942754</t>
+          <t xml:space="preserve">2119589</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F47">
-        <v>539</v>
+        <v>667</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590434</t>
+          <t xml:space="preserve">311590105</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-04</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F48">
-        <v>495</v>
+        <v>1323</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2436,11 +2436,11 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F49">
-        <v>958</v>
+        <v>539</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2486,11 +2486,11 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F50">
-        <v>618</v>
+        <v>495</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2536,11 +2536,11 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F51">
-        <v>1436</v>
+        <v>958</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2586,11 +2586,11 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F52">
-        <v>793</v>
+        <v>618</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2636,11 +2636,11 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F53">
-        <v>1312</v>
+        <v>1436</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2681,25 +2681,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302727</t>
+          <t xml:space="preserve">7942754</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F54">
-        <v>3054</v>
+        <v>793</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592650</t>
+          <t xml:space="preserve">311590434</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-12</t>
+          <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,25 +2731,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302727</t>
+          <t xml:space="preserve">7942754</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F55">
-        <v>396</v>
+        <v>1312</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592653</t>
+          <t xml:space="preserve">311590434</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-12</t>
+          <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2786,11 +2786,11 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F56">
-        <v>1186</v>
+        <v>3054</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2836,15 +2836,15 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F57">
-        <v>3640</v>
+        <v>396</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592650</t>
+          <t xml:space="preserve">311592653</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2886,15 +2886,15 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F58">
-        <v>772</v>
+        <v>1186</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592651</t>
+          <t xml:space="preserve">311592650</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2936,11 +2936,11 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F59">
-        <v>413</v>
+        <v>3640</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2981,20 +2981,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119886</t>
+          <t xml:space="preserve">1302727</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F60">
-        <v>678</v>
+        <v>772</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592656</t>
+          <t xml:space="preserve">311592651</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3031,20 +3031,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119886</t>
+          <t xml:space="preserve">1302727</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F61">
-        <v>1542</v>
+        <v>413</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592655</t>
+          <t xml:space="preserve">311592650</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3086,11 +3086,11 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F62">
-        <v>484</v>
+        <v>678</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3131,25 +3131,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2117120</t>
+          <t xml:space="preserve">2119886</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F63">
-        <v>442</v>
+        <v>1542</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610659</t>
+          <t xml:space="preserve">311592655</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-27</t>
+          <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,25 +3181,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2117120</t>
+          <t xml:space="preserve">2119886</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F64">
-        <v>1386</v>
+        <v>484</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610652</t>
+          <t xml:space="preserve">311592656</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-27</t>
+          <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3231,20 +3231,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2117690</t>
+          <t xml:space="preserve">2117120</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F65">
-        <v>297</v>
+        <v>442</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610625</t>
+          <t xml:space="preserve">311610659</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3281,20 +3281,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118930</t>
+          <t xml:space="preserve">2117120</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F66">
-        <v>960</v>
+        <v>1386</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610612</t>
+          <t xml:space="preserve">311610652</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120585</t>
+          <t xml:space="preserve">2117690</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3340,11 +3340,11 @@
         </is>
       </c>
       <c r="F67">
-        <v>441</v>
+        <v>297</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610605</t>
+          <t xml:space="preserve">311610625</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120587</t>
+          <t xml:space="preserve">2118930</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3390,11 +3390,11 @@
         </is>
       </c>
       <c r="F68">
-        <v>914</v>
+        <v>960</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610622</t>
+          <t xml:space="preserve">311610612</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120631</t>
+          <t xml:space="preserve">2120585</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3440,11 +3440,11 @@
         </is>
       </c>
       <c r="F69">
-        <v>324</v>
+        <v>441</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610628</t>
+          <t xml:space="preserve">311610605</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3481,20 +3481,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120631</t>
+          <t xml:space="preserve">2120587</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F70">
-        <v>360</v>
+        <v>914</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610626</t>
+          <t xml:space="preserve">311610622</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">7114712</t>
+          <t xml:space="preserve">2120631</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3540,11 +3540,11 @@
         </is>
       </c>
       <c r="F71">
-        <v>1929</v>
+        <v>324</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610614</t>
+          <t xml:space="preserve">311610628</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">8728328</t>
+          <t xml:space="preserve">2120631</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F72">
-        <v>9314</v>
+        <v>360</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656806</t>
+          <t xml:space="preserve">311610626</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-27</t>
+          <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120620</t>
+          <t xml:space="preserve">7114712</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3640,16 +3640,16 @@
         </is>
       </c>
       <c r="F73">
-        <v>561</v>
+        <v>1929</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311639469</t>
+          <t xml:space="preserve">311610614</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-01</t>
+          <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120620</t>
+          <t xml:space="preserve">8728328</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F74">
-        <v>412</v>
+        <v>9314</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311639470</t>
+          <t xml:space="preserve">311656806</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-01</t>
+          <t xml:space="preserve">2032-10-27</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3736,15 +3736,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F75">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311639471</t>
+          <t xml:space="preserve">311639468</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3781,25 +3781,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119309</t>
+          <t xml:space="preserve">2120620</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F76">
-        <v>1120</v>
+        <v>412</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311640302</t>
+          <t xml:space="preserve">311639468</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-03</t>
+          <t xml:space="preserve">2032-11-01</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,25 +3831,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119395</t>
+          <t xml:space="preserve">2120620</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F77">
-        <v>788</v>
+        <v>698</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311640295</t>
+          <t xml:space="preserve">311639468</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-03</t>
+          <t xml:space="preserve">2032-11-01</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120380</t>
+          <t xml:space="preserve">2120620</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F78">
-        <v>708</v>
+        <v>565</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311640296</t>
+          <t xml:space="preserve">311639468</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-03</t>
+          <t xml:space="preserve">2032-11-01</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,20 +3931,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120380</t>
+          <t xml:space="preserve">2119309</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F79">
-        <v>352</v>
+        <v>1120</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311640300</t>
+          <t xml:space="preserve">311640302</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3981,25 +3981,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118904</t>
+          <t xml:space="preserve">2119395</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F80">
-        <v>327</v>
+        <v>788</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642650</t>
+          <t xml:space="preserve">311640295</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-15</t>
+          <t xml:space="preserve">2032-11-03</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118904</t>
+          <t xml:space="preserve">2120380</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F81">
-        <v>297</v>
+        <v>708</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642650</t>
+          <t xml:space="preserve">311640296</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-15</t>
+          <t xml:space="preserve">2032-11-03</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,25 +4081,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118905</t>
+          <t xml:space="preserve">2120380</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F82">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642647</t>
+          <t xml:space="preserve">311640298</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-15</t>
+          <t xml:space="preserve">2032-11-03</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,20 +4131,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118905</t>
+          <t xml:space="preserve">2118904</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F83">
-        <v>361</v>
+        <v>327</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642652</t>
+          <t xml:space="preserve">311642650</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4181,20 +4181,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118932</t>
+          <t xml:space="preserve">2118904</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F84">
-        <v>789</v>
+        <v>297</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642584</t>
+          <t xml:space="preserve">311642650</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120628</t>
+          <t xml:space="preserve">2118905</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4240,11 +4240,11 @@
         </is>
       </c>
       <c r="F85">
-        <v>631</v>
+        <v>341</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642578</t>
+          <t xml:space="preserve">311642647</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9767631</t>
+          <t xml:space="preserve">2118905</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4290,11 +4290,11 @@
         </is>
       </c>
       <c r="F86">
-        <v>970</v>
+        <v>361</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642653</t>
+          <t xml:space="preserve">311642652</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119383</t>
+          <t xml:space="preserve">2118932</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="F87">
-        <v>2545</v>
+        <v>789</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646384</t>
+          <t xml:space="preserve">311642584</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-01</t>
+          <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">226330, 226331, 226332</t>
+          <t xml:space="preserve">2120628</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4390,16 +4390,16 @@
         </is>
       </c>
       <c r="F88">
-        <v>784</v>
+        <v>631</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646387</t>
+          <t xml:space="preserve">311642578</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-01</t>
+          <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302664</t>
+          <t xml:space="preserve">9767631</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F89">
-        <v>3245</v>
+        <v>970</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311648515</t>
+          <t xml:space="preserve">311642653</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-12</t>
+          <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302664</t>
+          <t xml:space="preserve">2119383</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F90">
-        <v>608</v>
+        <v>2545</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311648515</t>
+          <t xml:space="preserve">311646384</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-12</t>
+          <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4536,11 +4536,11 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F91">
-        <v>1394</v>
+        <v>3245</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4581,20 +4581,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119333</t>
+          <t xml:space="preserve">1302664</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F92">
-        <v>4109</v>
+        <v>608</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311648516</t>
+          <t xml:space="preserve">311648515</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4631,25 +4631,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119766</t>
+          <t xml:space="preserve">1302664</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F93">
-        <v>254</v>
+        <v>1394</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651636</t>
+          <t xml:space="preserve">311648515</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-27</t>
+          <t xml:space="preserve">2032-12-12</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119885</t>
+          <t xml:space="preserve">2119333</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4690,16 +4690,16 @@
         </is>
       </c>
       <c r="F94">
-        <v>418</v>
+        <v>4109</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651634</t>
+          <t xml:space="preserve">311648516</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-27</t>
+          <t xml:space="preserve">2032-12-12</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">227307, 227308, 227309, 227310, 227311, 227312</t>
+          <t xml:space="preserve">2119766</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4740,11 +4740,11 @@
         </is>
       </c>
       <c r="F95">
-        <v>584</v>
+        <v>254</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651635</t>
+          <t xml:space="preserve">311651636</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121201</t>
+          <t xml:space="preserve">2119885</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4790,16 +4790,16 @@
         </is>
       </c>
       <c r="F96">
-        <v>4686</v>
+        <v>418</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653652</t>
+          <t xml:space="preserve">311651634</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-12</t>
+          <t xml:space="preserve">2032-12-27</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4836,15 +4836,15 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F97">
-        <v>3374</v>
+        <v>4686</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653656</t>
+          <t xml:space="preserve">311653652</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4881,25 +4881,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121205</t>
+          <t xml:space="preserve">2121201</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F98">
-        <v>2013</v>
+        <v>3374</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311662689</t>
+          <t xml:space="preserve">311653656</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-27</t>
+          <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">228152, 228153</t>
+          <t xml:space="preserve">2121205</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4940,11 +4940,11 @@
         </is>
       </c>
       <c r="F99">
-        <v>1744</v>
+        <v>2013</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311662687</t>
+          <t xml:space="preserve">311662689</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">226855, 226856</t>
+          <t xml:space="preserve">712017, 2120435</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F104">
-        <v>1125</v>
+        <v>254</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311691228</t>
+          <t xml:space="preserve">311683592</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-28</t>
+          <t xml:space="preserve">2033-05-26</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311798616</t>
+          <t xml:space="preserve">311798611</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5431,25 +5431,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">229532, 229533, 229534</t>
+          <t xml:space="preserve">2120299</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F109">
-        <v>9132</v>
+        <v>858</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311870463</t>
+          <t xml:space="preserve">311869006</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-27</t>
+          <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">

--- a/public/exports/65120119.xlsx
+++ b/public/exports/65120119.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:L109"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Statenevej 46</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2117868</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>548</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dommervangen 4</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">2121205</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>624</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sofielundsvej 120</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">2121754</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>339</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Toftevej 6</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">226330, 226331, 226332</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>784</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestergårdsvej 16A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">226855, 226856</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>1125</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kærmindevej 5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">227307, 227308, 227309, 227310, 227311, 227312</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>584</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Asylvej 1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">228152, 228153</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>1744</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhusparken 1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">229532, 229533, 229534</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>9132</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ejby Mosevej 15</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">2117657</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>457</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">200011133</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-03-03</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Christiansvej 3</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119016</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>338</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">200018781</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-08-17</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestervej 19</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">2118940</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>1098</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">200020473</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bakken 5</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2118905</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>257</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">200020916</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-22</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Asylvej 29</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">7910620</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>1418</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">311037217</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-02-07</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sofielundsvej 120</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">1302727</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">33</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>1991</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">311266310</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-15</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dommervangen 1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2121204</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>2582</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">311316443</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-05-25</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paul Bergsøes Vej 37</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2121011</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>721</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">311353004</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-12-23</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedvejen 134</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2118050</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>485</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">311548536</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-16</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ved Brandstationen 1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2120377</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>1498</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">311586001</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-07</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 81</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119099</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>370</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311588705</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311588706</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 81</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119099</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>370</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311588705</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311588706</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 81</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119099</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>370</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311588705</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311588706</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 81</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119099</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>1140</v>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311588705</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311588706</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 81</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119099</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>1394</v>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311588705</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311588706</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 81</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119099</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>499</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311588705</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311588706</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 81</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119099</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>409</v>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311588705</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311588706</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 81</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119099</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>356</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311588705</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311588706</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 81</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119099</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>2026</v>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311588705</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311588706</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 81</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119099</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>1968</v>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311588705</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311588706</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 81</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119099</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>1175</v>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311588705</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311588706</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 81</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119099</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>997</v>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311588705</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311588706</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Callisensvej 34</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2900</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2018964</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>321</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">311588707</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ejby Torvevej 13</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2117851</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>1941</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">311588724</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Florasvej 2</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119886</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>410</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">311588725</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Florasvej 2</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119886</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>472</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">311588725</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Florasvej 2</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119886</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>1892</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">311588725</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Florasvej 2</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119886</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>1678</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">311588725</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Florasvej 2</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119886</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>3639</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">311588725</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Florasvej 2</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119886</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>499</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311588725</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Essedal 12</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">100040948</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>1186</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">311590092</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Statenevej 1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2117855</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>567</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">311590100</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Statenevej 1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2117855</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>591</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">311590100</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 80</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2118958</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>4333</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">311590114</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 80</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2118958</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>386</v>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311590111</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311590114</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 80</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2118958</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>1122</v>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311590114</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311590120</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 80</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2118958</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>2621</v>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311590114</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311590120</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ørnebjergvej 10</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119589</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>667</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">311590105</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egeskoven 27</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">7942754</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>1323</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">311590434</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egeskoven 27</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">7942754</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>539</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">311590434</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egeskoven 27</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">7942754</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>495</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">311590434</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egeskoven 27</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">7942754</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>958</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">311590434</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egeskoven 27</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">7942754</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>618</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">311590434</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egeskoven 27</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">7942754</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">20</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>1436</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">311590434</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egeskoven 27</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">7942754</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>793</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">311590434</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2731,33 +3271,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egeskoven 27</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">7942754</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>1312</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">311590434</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2781,33 +3331,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sofielundsvej 120</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">1302727</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>3054</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">311592650</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2831,33 +3391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sofielundsvej 120</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">1302727</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>396</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">311592653</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2881,33 +3451,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sofielundsvej 120</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">1302727</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>1186</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">311592650</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2931,33 +3511,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sofielundsvej 120</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">1302727</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>3640</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">311592650</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2981,33 +3571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sofielundsvej 120</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">1302727</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>772</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">311592651</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3031,33 +3631,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sofielundsvej 120</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">1302727</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>413</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">311592650</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,33 +3691,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Florasvej 2B</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119886</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>678</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">311592656</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3131,33 +3751,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Florasvej 2</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119886</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>1542</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">311592655</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3181,33 +3811,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Florasvej 2A</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119886</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>484</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">311592656</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3231,33 +3871,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mosetoften 35</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2117120</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>442</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">311610659</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3281,33 +3931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mosetoften 35</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2117120</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>1386</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">311610652</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3331,33 +3991,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ejby Mosevej 13</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2117690</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>297</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">311610625</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3381,33 +4051,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestervej 25A</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2118930</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>960</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">311610612</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3431,33 +4111,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stenager 191</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2120585</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>441</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">311610605</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3481,33 +4171,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Granskoven 169</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2120587</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>914</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">311610622</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3531,33 +4231,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vældegårdsvej 30</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2120631</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F71">
+      <c r="H71">
         <v>324</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">311610628</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3581,33 +4291,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vældegårdsvej 30</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2120631</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F72">
+      <c r="H72">
         <v>360</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">311610626</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3631,33 +4351,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egeskoven 25</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">7114712</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F73">
+      <c r="H73">
         <v>1929</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">311610614</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3681,33 +4411,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Christiansvej 2</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">8728328</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="H74">
         <v>9314</v>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">311656806</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-10-27</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3731,33 +4471,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvissingegade 15A</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2120620</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F75">
+      <c r="H75">
         <v>561</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">311639468</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-01</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3781,33 +4531,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvissingegade 17</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2120620</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="F76">
+      <c r="H76">
         <v>412</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">311639468</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-01</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3831,33 +4591,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvissingegade 15</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2120620</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>698</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">311639468</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-01</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3881,33 +4651,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvissingegade 19</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2120620</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>565</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">311639468</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-01</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3931,33 +4711,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhusparken 4</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119309</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F79">
+      <c r="H79">
         <v>1120</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">311640302</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-03</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3981,33 +4771,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kildevældets Alle 8</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119395</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>788</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">311640295</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-03</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4031,33 +4831,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ved Brandstationen 2</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2120380</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F81">
+      <c r="H81">
         <v>708</v>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311640296</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311640298</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-03</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4081,33 +4891,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kildevej 8</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2120380</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="H82">
         <v>352</v>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">311640298</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-03</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4131,33 +4951,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bakken 9</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2118904</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F83">
+      <c r="H83">
         <v>327</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">311642650</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4181,33 +5011,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bakken 11</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2118904</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F84">
+      <c r="H84">
         <v>297</v>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">311642650</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4231,33 +5071,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bakken 1</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2118905</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F85">
+      <c r="H85">
         <v>341</v>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t xml:space="preserve">311642647</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4281,33 +5131,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bakken 3</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2118905</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F86">
+      <c r="H86">
         <v>361</v>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">311642652</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4331,33 +5191,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bryggergårdsvej 2C</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2118932</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F87">
+      <c r="H87">
         <v>789</v>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">311642584</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4381,33 +5251,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bøgeskoven 203</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2120628</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F88">
+      <c r="H88">
         <v>631</v>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t xml:space="preserve">311642578</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4431,33 +5311,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bakken 2</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t xml:space="preserve">9767631</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F89">
+      <c r="H89">
         <v>970</v>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t xml:space="preserve">311642653</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4481,33 +5371,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kildevældets Alle 5</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119383</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F90">
+      <c r="H90">
         <v>2545</v>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">311646384</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4531,33 +5431,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhusparken 2</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t xml:space="preserve">1302664</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F91">
+      <c r="H91">
         <v>3245</v>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t xml:space="preserve">311648515</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-12</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4581,33 +5491,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhusparken 2</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t xml:space="preserve">1302664</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F92">
+      <c r="H92">
         <v>608</v>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t xml:space="preserve">311648515</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-12</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4631,33 +5551,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhusparken 2</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t xml:space="preserve">1302664</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F93">
+      <c r="H93">
         <v>1394</v>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t xml:space="preserve">311648515</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-12</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4681,33 +5611,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sydvestvej 10</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119333</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F94">
+      <c r="H94">
         <v>4109</v>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t xml:space="preserve">311648516</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-12</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
+      <c r="K94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4731,33 +5671,43 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedvejen 97</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119766</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F95">
+      <c r="H95">
         <v>254</v>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t xml:space="preserve">311651636</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-27</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4781,33 +5731,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedvejen 51</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119885</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F96">
+      <c r="H96">
         <v>418</v>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t xml:space="preserve">311651634</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-12-27</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
+      <c r="K96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4831,33 +5791,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Digevangsvej 1</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2121201</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F97">
+      <c r="H97">
         <v>4686</v>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t xml:space="preserve">311653652</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
+      <c r="K97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4881,33 +5851,43 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Digevangsvej 1</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2121201</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F98">
+      <c r="H98">
         <v>3374</v>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t xml:space="preserve">311653656</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
+      <c r="K98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4931,33 +5911,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dommervangen 4</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2121205</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F99">
+      <c r="H99">
         <v>2013</v>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t xml:space="preserve">311662689</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-02-27</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
+      <c r="K99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4981,33 +5971,43 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bøgeskoven 4</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t xml:space="preserve">7942754</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F100">
+      <c r="H100">
         <v>498</v>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t xml:space="preserve">311662694</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-02-27</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
+      <c r="K100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5031,33 +6031,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bøgeskoven 2</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t xml:space="preserve">7942754</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>596</v>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t xml:space="preserve">311662692</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-02-27</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
+      <c r="K101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5081,33 +6091,43 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stenager 2</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t xml:space="preserve">9905315</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F102">
+      <c r="H102">
         <v>7139</v>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t xml:space="preserve">311662695</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-02-27</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
+      <c r="K102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5131,33 +6151,43 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Statenevej 46</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2117868</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F103">
+      <c r="H103">
         <v>309</v>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t xml:space="preserve">311683595</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-26</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
+      <c r="K103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5181,33 +6211,43 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Solvangsvej 26A</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t xml:space="preserve">712017, 2120435</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F104">
+      <c r="H104">
         <v>254</v>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t xml:space="preserve">311683592</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-26</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
+      <c r="K104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5231,33 +6271,43 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Digevangsvej 5</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2121201</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F105">
+      <c r="H105">
         <v>1609</v>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t xml:space="preserve">311739998</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-02-20</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
+      <c r="K105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5281,33 +6331,43 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Eriksvej 22</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2119215</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F106">
+      <c r="H106">
         <v>1542</v>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t xml:space="preserve">311751667</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-04-12</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
+      <c r="K106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5331,33 +6391,43 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hvissingevej 63B</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t xml:space="preserve">100040949</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F107">
+      <c r="H107">
         <v>431</v>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t xml:space="preserve">311794959</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-01</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
+      <c r="K107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5381,33 +6451,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Byparkvej 87</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2121572</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F108">
+      <c r="H108">
         <v>4798</v>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311798611</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
+      <c r="I108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311798613</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-21</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
+      <c r="K108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5431,39 +6511,49 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndervangsvej 90</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2120299</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F109">
+      <c r="H109">
         <v>858</v>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t xml:space="preserve">311869006</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
+      <c r="K109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J109"/>
+  <autoFilter ref="A1:L109"/>
 </worksheet>
 </file>
--- a/public/exports/65120119.xlsx
+++ b/public/exports/65120119.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statenevej 46</t>
+          <t xml:space="preserve">Dommervangen 4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,16 +101,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2117868</t>
+          <t xml:space="preserve">2121205</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H2">
-        <v>548</v>
+        <v>624</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dommervangen 4</t>
+          <t xml:space="preserve">Sofielundsvej 120</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121205</t>
+          <t xml:space="preserve">2121754</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H3">
-        <v>624</v>
+        <v>339</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofielundsvej 120</t>
+          <t xml:space="preserve">Statenevej 46</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,16 +221,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121754</t>
+          <t xml:space="preserve">2117868</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H4">
-        <v>339</v>
+        <v>548</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftevej 6</t>
+          <t xml:space="preserve">Ejby Mosevej 15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,7 +281,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">226330, 226331, 226332</t>
+          <t xml:space="preserve">2117657</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -290,21 +290,21 @@
         </is>
       </c>
       <c r="H5">
-        <v>784</v>
+        <v>457</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011133</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-03</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergårdsvej 16A</t>
+          <t xml:space="preserve">Christiansvej 3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,7 +341,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">226855, 226856</t>
+          <t xml:space="preserve">2119016</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -350,21 +350,21 @@
         </is>
       </c>
       <c r="H6">
-        <v>1125</v>
+        <v>338</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200018781</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-08-17</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærmindevej 5</t>
+          <t xml:space="preserve">Vestervej 19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,7 +401,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">227307, 227308, 227309, 227310, 227311, 227312</t>
+          <t xml:space="preserve">2118940</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -410,21 +410,21 @@
         </is>
       </c>
       <c r="H7">
-        <v>584</v>
+        <v>1098</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200020473</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asylvej 1</t>
+          <t xml:space="preserve">Bakken 5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,30 +461,30 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">228152, 228153</t>
+          <t xml:space="preserve">2118905</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H8">
-        <v>1744</v>
+        <v>257</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200020916</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusparken 1</t>
+          <t xml:space="preserve">Asylvej 29</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">229532, 229533, 229534</t>
+          <t xml:space="preserve">7910620</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -530,21 +530,21 @@
         </is>
       </c>
       <c r="H9">
-        <v>9132</v>
+        <v>1418</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311037217</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-02-07</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejby Mosevej 15</t>
+          <t xml:space="preserve">Sofielundsvej 120</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,35 +581,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2117657</t>
+          <t xml:space="preserve">1302727</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="H10">
-        <v>457</v>
+        <v>1991</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011133</t>
+          <t xml:space="preserve">311266310</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-03</t>
+          <t xml:space="preserve">2027-08-15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christiansvej 3</t>
+          <t xml:space="preserve">Dommervangen 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,35 +641,35 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119016</t>
+          <t xml:space="preserve">2121204</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H11">
-        <v>338</v>
+        <v>2582</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018781</t>
+          <t xml:space="preserve">311316443</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-17</t>
+          <t xml:space="preserve">2028-05-25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervej 19</t>
+          <t xml:space="preserve">Paul Bergsøes Vej 37</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,35 +701,35 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118940</t>
+          <t xml:space="preserve">2121011</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H12">
-        <v>1098</v>
+        <v>721</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020473</t>
+          <t xml:space="preserve">311353004</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2028-12-23</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakken 5</t>
+          <t xml:space="preserve">Hovedvejen 134</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,35 +761,35 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118905</t>
+          <t xml:space="preserve">2118050</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H13">
-        <v>257</v>
+        <v>485</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020916</t>
+          <t xml:space="preserve">311548536</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-22</t>
+          <t xml:space="preserve">2031-09-16</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asylvej 29</t>
+          <t xml:space="preserve">Ved Brandstationen 1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">7910620</t>
+          <t xml:space="preserve">2120377</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -830,26 +830,26 @@
         </is>
       </c>
       <c r="H14">
-        <v>1418</v>
+        <v>1498</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">311037217</t>
+          <t xml:space="preserve">311586001</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-02-07</t>
+          <t xml:space="preserve">2031-12-07</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofielundsvej 120</t>
+          <t xml:space="preserve">Stadionvej 81</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -881,25 +881,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302727</t>
+          <t xml:space="preserve">2119099</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H15">
-        <v>1991</v>
+        <v>370</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266310</t>
+          <t xml:space="preserve">311588706</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-15</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dommervangen 1</t>
+          <t xml:space="preserve">Stadionvej 81</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,25 +941,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121204</t>
+          <t xml:space="preserve">2119099</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H16">
-        <v>2582</v>
+        <v>370</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311316443</t>
+          <t xml:space="preserve">311588706</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-25</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paul Bergsøes Vej 37</t>
+          <t xml:space="preserve">Stadionvej 81</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1001,25 +1001,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121011</t>
+          <t xml:space="preserve">2119099</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H17">
-        <v>721</v>
+        <v>370</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311353004</t>
+          <t xml:space="preserve">311588706</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-23</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 134</t>
+          <t xml:space="preserve">Stadionvej 81</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,25 +1061,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118050</t>
+          <t xml:space="preserve">2119099</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H18">
-        <v>485</v>
+        <v>1140</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548536</t>
+          <t xml:space="preserve">311588706</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-16</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Brandstationen 1</t>
+          <t xml:space="preserve">Stadionvej 81</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,25 +1121,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120377</t>
+          <t xml:space="preserve">2119099</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H19">
-        <v>1498</v>
+        <v>1394</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586001</t>
+          <t xml:space="preserve">311588706</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-07</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1186,11 +1186,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H20">
-        <v>370</v>
+        <v>499</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1246,11 +1246,11 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H21">
-        <v>370</v>
+        <v>409</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1306,11 +1306,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H22">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1366,11 +1366,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H23">
-        <v>1140</v>
+        <v>2026</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1426,11 +1426,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H24">
-        <v>1394</v>
+        <v>1968</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1486,11 +1486,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H25">
-        <v>499</v>
+        <v>1175</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1546,11 +1546,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H26">
-        <v>409</v>
+        <v>997</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1586,40 +1586,40 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">161</t>
+          <t xml:space="preserve">157</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 81</t>
+          <t xml:space="preserve">Callisensvej 34</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2600</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119099</t>
+          <t xml:space="preserve">2018964</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H27">
-        <v>356</v>
+        <v>321</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588707</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-09</t>
+          <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 81</t>
+          <t xml:space="preserve">Ejby Torvevej 13</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,25 +1661,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119099</t>
+          <t xml:space="preserve">2117851</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H28">
-        <v>2026</v>
+        <v>1941</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588724</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-09</t>
+          <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 81</t>
+          <t xml:space="preserve">Florasvej 2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,25 +1721,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119099</t>
+          <t xml:space="preserve">2119886</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H29">
-        <v>1968</v>
+        <v>410</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588725</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-09</t>
+          <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 81</t>
+          <t xml:space="preserve">Florasvej 2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,25 +1781,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119099</t>
+          <t xml:space="preserve">2119886</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H30">
-        <v>1175</v>
+        <v>472</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588725</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-09</t>
+          <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 81</t>
+          <t xml:space="preserve">Florasvej 2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,25 +1841,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119099</t>
+          <t xml:space="preserve">2119886</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H31">
-        <v>997</v>
+        <v>1892</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588725</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-09</t>
+          <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -1886,35 +1886,35 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">157</t>
+          <t xml:space="preserve">161</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Callisensvej 34</t>
+          <t xml:space="preserve">Florasvej 2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2600</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018964</t>
+          <t xml:space="preserve">2119886</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H32">
-        <v>321</v>
+        <v>1678</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588707</t>
+          <t xml:space="preserve">311588725</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejby Torvevej 13</t>
+          <t xml:space="preserve">Florasvej 2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1961,20 +1961,20 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2117851</t>
+          <t xml:space="preserve">2119886</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H33">
-        <v>1941</v>
+        <v>3639</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588724</t>
+          <t xml:space="preserve">311588725</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2026,11 +2026,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H34">
-        <v>410</v>
+        <v>499</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Florasvej 2</t>
+          <t xml:space="preserve">Essedal 12</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2081,25 +2081,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119886</t>
+          <t xml:space="preserve">100040948</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H35">
-        <v>472</v>
+        <v>1186</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588725</t>
+          <t xml:space="preserve">311590092</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Florasvej 2</t>
+          <t xml:space="preserve">Stadionvej 80</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,25 +2141,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119886</t>
+          <t xml:space="preserve">2118958</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H36">
-        <v>1892</v>
+        <v>4333</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588725</t>
+          <t xml:space="preserve">311590123</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Florasvej 2</t>
+          <t xml:space="preserve">Stadionvej 80</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2201,25 +2201,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119886</t>
+          <t xml:space="preserve">2118958</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H37">
-        <v>1678</v>
+        <v>386</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588725</t>
+          <t xml:space="preserve">311590111</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Florasvej 2</t>
+          <t xml:space="preserve">Stadionvej 80</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2261,25 +2261,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119886</t>
+          <t xml:space="preserve">2118958</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H38">
-        <v>3639</v>
+        <v>1122</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588725</t>
+          <t xml:space="preserve">311590120</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Florasvej 2</t>
+          <t xml:space="preserve">Stadionvej 80</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2321,25 +2321,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119886</t>
+          <t xml:space="preserve">2118958</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H39">
-        <v>499</v>
+        <v>2621</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588725</t>
+          <t xml:space="preserve">311590120</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Essedal 12</t>
+          <t xml:space="preserve">Statenevej 1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">100040948</t>
+          <t xml:space="preserve">2117855</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2390,11 +2390,11 @@
         </is>
       </c>
       <c r="H40">
-        <v>1186</v>
+        <v>567</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590092</t>
+          <t xml:space="preserve">311590100</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2446,11 +2446,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H41">
-        <v>567</v>
+        <v>591</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statenevej 1</t>
+          <t xml:space="preserve">Ørnebjergvej 10</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,20 +2501,20 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2117855</t>
+          <t xml:space="preserve">2119589</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H42">
-        <v>591</v>
+        <v>667</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590100</t>
+          <t xml:space="preserve">311590105</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 80</t>
+          <t xml:space="preserve">Egeskoven 27</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118958</t>
+          <t xml:space="preserve">7942754</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2570,16 +2570,16 @@
         </is>
       </c>
       <c r="H43">
-        <v>4333</v>
+        <v>1323</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590114</t>
+          <t xml:space="preserve">311590434</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 80</t>
+          <t xml:space="preserve">Egeskoven 27</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,25 +2621,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118958</t>
+          <t xml:space="preserve">7942754</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H44">
-        <v>386</v>
+        <v>539</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590114</t>
+          <t xml:space="preserve">311590434</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 80</t>
+          <t xml:space="preserve">Egeskoven 27</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2681,25 +2681,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118958</t>
+          <t xml:space="preserve">7942754</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H45">
-        <v>1122</v>
+        <v>495</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590120</t>
+          <t xml:space="preserve">311590434</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 80</t>
+          <t xml:space="preserve">Egeskoven 27</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2741,25 +2741,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118958</t>
+          <t xml:space="preserve">7942754</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H46">
-        <v>2621</v>
+        <v>958</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590120</t>
+          <t xml:space="preserve">311590434</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnebjergvej 10</t>
+          <t xml:space="preserve">Egeskoven 27</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2801,25 +2801,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119589</t>
+          <t xml:space="preserve">7942754</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H47">
-        <v>667</v>
+        <v>618</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590105</t>
+          <t xml:space="preserve">311590434</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-01</t>
+          <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2866,11 +2866,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H48">
-        <v>1323</v>
+        <v>1436</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2926,11 +2926,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H49">
-        <v>539</v>
+        <v>793</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2986,11 +2986,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H50">
-        <v>495</v>
+        <v>1312</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeskoven 27</t>
+          <t xml:space="preserve">Florasvej 2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,25 +3041,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7942754</t>
+          <t xml:space="preserve">2119886</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H51">
-        <v>958</v>
+        <v>1542</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590434</t>
+          <t xml:space="preserve">311592655</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-04</t>
+          <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeskoven 27</t>
+          <t xml:space="preserve">Florasvej 2A</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3101,25 +3101,25 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">7942754</t>
+          <t xml:space="preserve">2119886</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H52">
-        <v>618</v>
+        <v>484</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590434</t>
+          <t xml:space="preserve">311592656</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-04</t>
+          <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeskoven 27</t>
+          <t xml:space="preserve">Florasvej 2B</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3161,25 +3161,25 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">7942754</t>
+          <t xml:space="preserve">2119886</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H53">
-        <v>1436</v>
+        <v>678</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590434</t>
+          <t xml:space="preserve">311592656</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-04</t>
+          <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeskoven 27</t>
+          <t xml:space="preserve">Sofielundsvej 120</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3221,25 +3221,25 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7942754</t>
+          <t xml:space="preserve">1302727</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H54">
-        <v>793</v>
+        <v>3054</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590434</t>
+          <t xml:space="preserve">311592650</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-04</t>
+          <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeskoven 27</t>
+          <t xml:space="preserve">Sofielundsvej 120</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7942754</t>
+          <t xml:space="preserve">1302727</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H55">
-        <v>1312</v>
+        <v>396</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590434</t>
+          <t xml:space="preserve">311592653</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-04</t>
+          <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3346,11 +3346,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H56">
-        <v>3054</v>
+        <v>1186</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3406,15 +3406,15 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H57">
-        <v>396</v>
+        <v>3640</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592653</t>
+          <t xml:space="preserve">311592650</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3466,15 +3466,15 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H58">
-        <v>1186</v>
+        <v>772</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592650</t>
+          <t xml:space="preserve">311592651</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3526,11 +3526,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H59">
-        <v>3640</v>
+        <v>413</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofielundsvej 120</t>
+          <t xml:space="preserve">Egeskoven 25</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302727</t>
+          <t xml:space="preserve">7114712</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H60">
-        <v>772</v>
+        <v>1929</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592651</t>
+          <t xml:space="preserve">311610614</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-12</t>
+          <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofielundsvej 120</t>
+          <t xml:space="preserve">Ejby Mosevej 13</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3641,25 +3641,25 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302727</t>
+          <t xml:space="preserve">2117690</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H61">
-        <v>413</v>
+        <v>297</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592650</t>
+          <t xml:space="preserve">311610625</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-12</t>
+          <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Florasvej 2B</t>
+          <t xml:space="preserve">Granskoven 169</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3701,25 +3701,25 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119886</t>
+          <t xml:space="preserve">2120587</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H62">
-        <v>678</v>
+        <v>914</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592656</t>
+          <t xml:space="preserve">311610622</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-12</t>
+          <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Florasvej 2</t>
+          <t xml:space="preserve">Mosetoften 35</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3761,25 +3761,25 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119886</t>
+          <t xml:space="preserve">2117120</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H63">
-        <v>1542</v>
+        <v>442</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592655</t>
+          <t xml:space="preserve">311610659</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-12</t>
+          <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Florasvej 2A</t>
+          <t xml:space="preserve">Mosetoften 35</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3821,25 +3821,25 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119886</t>
+          <t xml:space="preserve">2117120</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H64">
-        <v>484</v>
+        <v>1386</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592656</t>
+          <t xml:space="preserve">311610652</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-12</t>
+          <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosetoften 35</t>
+          <t xml:space="preserve">Stenager 191</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3881,20 +3881,20 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2117120</t>
+          <t xml:space="preserve">2120585</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H65">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610659</t>
+          <t xml:space="preserve">311610605</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosetoften 35</t>
+          <t xml:space="preserve">Vestervej 25A</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,20 +3941,20 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2117120</t>
+          <t xml:space="preserve">2118930</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H66">
-        <v>1386</v>
+        <v>960</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610652</t>
+          <t xml:space="preserve">311610612</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejby Mosevej 13</t>
+          <t xml:space="preserve">Vældegårdsvej 30</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2117690</t>
+          <t xml:space="preserve">2120631</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4010,11 +4010,11 @@
         </is>
       </c>
       <c r="H67">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610625</t>
+          <t xml:space="preserve">311610628</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervej 25A</t>
+          <t xml:space="preserve">Vældegårdsvej 30</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4061,20 +4061,20 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118930</t>
+          <t xml:space="preserve">2120631</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H68">
-        <v>960</v>
+        <v>360</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610612</t>
+          <t xml:space="preserve">311610626</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenager 191</t>
+          <t xml:space="preserve">Christiansvej 2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120585</t>
+          <t xml:space="preserve">8728328</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="H69">
-        <v>441</v>
+        <v>9314</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610605</t>
+          <t xml:space="preserve">311656806</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-27</t>
+          <t xml:space="preserve">2032-10-27</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Granskoven 169</t>
+          <t xml:space="preserve">Hvissingegade 15</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120587</t>
+          <t xml:space="preserve">2120620</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H70">
-        <v>914</v>
+        <v>698</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610622</t>
+          <t xml:space="preserve">311639468</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-27</t>
+          <t xml:space="preserve">2032-11-01</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vældegårdsvej 30</t>
+          <t xml:space="preserve">Hvissingegade 15A</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120631</t>
+          <t xml:space="preserve">2120620</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4250,16 +4250,16 @@
         </is>
       </c>
       <c r="H71">
-        <v>324</v>
+        <v>561</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610628</t>
+          <t xml:space="preserve">311639469</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-27</t>
+          <t xml:space="preserve">2032-11-01</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vældegårdsvej 30</t>
+          <t xml:space="preserve">Hvissingegade 17</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4301,25 +4301,25 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120631</t>
+          <t xml:space="preserve">2120620</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H72">
-        <v>360</v>
+        <v>412</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610626</t>
+          <t xml:space="preserve">311639470</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-27</t>
+          <t xml:space="preserve">2032-11-01</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeskoven 25</t>
+          <t xml:space="preserve">Hvissingegade 19</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4361,25 +4361,25 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">7114712</t>
+          <t xml:space="preserve">2120620</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H73">
-        <v>1929</v>
+        <v>565</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610614</t>
+          <t xml:space="preserve">311639471</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-27</t>
+          <t xml:space="preserve">2032-11-01</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christiansvej 2</t>
+          <t xml:space="preserve">Kildevej 8</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4421,25 +4421,25 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">8728328</t>
+          <t xml:space="preserve">2120380</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H74">
-        <v>9314</v>
+        <v>352</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656806</t>
+          <t xml:space="preserve">311640300</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-27</t>
+          <t xml:space="preserve">2032-11-03</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvissingegade 15A</t>
+          <t xml:space="preserve">Kildevældets Alle 8</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120620</t>
+          <t xml:space="preserve">2119395</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="H75">
-        <v>561</v>
+        <v>788</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311639468</t>
+          <t xml:space="preserve">311640295</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-01</t>
+          <t xml:space="preserve">2032-11-03</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvissingegade 17</t>
+          <t xml:space="preserve">Rådhusparken 4</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4541,25 +4541,25 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120620</t>
+          <t xml:space="preserve">2119309</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H76">
-        <v>412</v>
+        <v>1120</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311639468</t>
+          <t xml:space="preserve">311640302</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-01</t>
+          <t xml:space="preserve">2032-11-03</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvissingegade 15</t>
+          <t xml:space="preserve">Ved Brandstationen 2</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4601,25 +4601,25 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120620</t>
+          <t xml:space="preserve">2120380</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H77">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311639468</t>
+          <t xml:space="preserve">311640296</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-01</t>
+          <t xml:space="preserve">2032-11-03</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvissingegade 19</t>
+          <t xml:space="preserve">Bakken 1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4661,25 +4661,25 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120620</t>
+          <t xml:space="preserve">2118905</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H78">
-        <v>565</v>
+        <v>341</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311639468</t>
+          <t xml:space="preserve">311642647</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-01</t>
+          <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusparken 4</t>
+          <t xml:space="preserve">Bakken 11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4721,25 +4721,25 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119309</t>
+          <t xml:space="preserve">2118904</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H79">
-        <v>1120</v>
+        <v>297</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311640302</t>
+          <t xml:space="preserve">311642650</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-03</t>
+          <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildevældets Alle 8</t>
+          <t xml:space="preserve">Bakken 2</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,25 +4781,25 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119395</t>
+          <t xml:space="preserve">9767631</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H80">
-        <v>788</v>
+        <v>970</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311640295</t>
+          <t xml:space="preserve">311642653</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-03</t>
+          <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Brandstationen 2</t>
+          <t xml:space="preserve">Bakken 3</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4841,25 +4841,25 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120380</t>
+          <t xml:space="preserve">2118905</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H81">
-        <v>708</v>
+        <v>361</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311640298</t>
+          <t xml:space="preserve">311642652</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-03</t>
+          <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildevej 8</t>
+          <t xml:space="preserve">Bakken 9</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,25 +4901,25 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120380</t>
+          <t xml:space="preserve">2118904</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H82">
-        <v>352</v>
+        <v>327</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311640298</t>
+          <t xml:space="preserve">311642650</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-03</t>
+          <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakken 9</t>
+          <t xml:space="preserve">Bryggergårdsvej 2C</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4961,20 +4961,20 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118904</t>
+          <t xml:space="preserve">2118932</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H83">
-        <v>327</v>
+        <v>789</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642650</t>
+          <t xml:space="preserve">311642584</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakken 11</t>
+          <t xml:space="preserve">Bøgeskoven 203</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5021,20 +5021,20 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118904</t>
+          <t xml:space="preserve">2120628</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H84">
-        <v>297</v>
+        <v>631</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642650</t>
+          <t xml:space="preserve">311642578</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakken 1</t>
+          <t xml:space="preserve">Kildevældets Alle 5</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118905</t>
+          <t xml:space="preserve">2119383</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5090,16 +5090,16 @@
         </is>
       </c>
       <c r="H85">
-        <v>341</v>
+        <v>2545</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642647</t>
+          <t xml:space="preserve">311646384</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-15</t>
+          <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakken 3</t>
+          <t xml:space="preserve">Toftevej 6</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5141,25 +5141,25 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118905</t>
+          <t xml:space="preserve">226330, 226331, 226332</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H86">
-        <v>361</v>
+        <v>784</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642652</t>
+          <t xml:space="preserve">311646387</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-15</t>
+          <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryggergårdsvej 2C</t>
+          <t xml:space="preserve">Rådhusparken 2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118932</t>
+          <t xml:space="preserve">1302664</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5210,16 +5210,16 @@
         </is>
       </c>
       <c r="H87">
-        <v>789</v>
+        <v>3245</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642584</t>
+          <t xml:space="preserve">311648515</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-15</t>
+          <t xml:space="preserve">2032-12-12</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgeskoven 203</t>
+          <t xml:space="preserve">Rådhusparken 2</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5261,25 +5261,25 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120628</t>
+          <t xml:space="preserve">1302664</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H88">
-        <v>631</v>
+        <v>608</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642578</t>
+          <t xml:space="preserve">311648515</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-15</t>
+          <t xml:space="preserve">2032-12-12</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakken 2</t>
+          <t xml:space="preserve">Rådhusparken 2</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5321,25 +5321,25 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9767631</t>
+          <t xml:space="preserve">1302664</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H89">
-        <v>970</v>
+        <v>1394</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642653</t>
+          <t xml:space="preserve">311648515</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-15</t>
+          <t xml:space="preserve">2032-12-12</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildevældets Alle 5</t>
+          <t xml:space="preserve">Sydvestvej 10</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119383</t>
+          <t xml:space="preserve">2119333</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5390,16 +5390,16 @@
         </is>
       </c>
       <c r="H90">
-        <v>2545</v>
+        <v>4109</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646384</t>
+          <t xml:space="preserve">311648516</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-01</t>
+          <t xml:space="preserve">2032-12-12</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusparken 2</t>
+          <t xml:space="preserve">Hovedvejen 51</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302664</t>
+          <t xml:space="preserve">2119885</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5450,16 +5450,16 @@
         </is>
       </c>
       <c r="H91">
-        <v>3245</v>
+        <v>418</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311648515</t>
+          <t xml:space="preserve">311651634</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-12</t>
+          <t xml:space="preserve">2032-12-27</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusparken 2</t>
+          <t xml:space="preserve">Hovedvejen 97</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5501,25 +5501,25 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302664</t>
+          <t xml:space="preserve">2119766</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H92">
-        <v>608</v>
+        <v>254</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311648515</t>
+          <t xml:space="preserve">311651636</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-12</t>
+          <t xml:space="preserve">2032-12-27</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusparken 2</t>
+          <t xml:space="preserve">Kærmindevej 5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5561,25 +5561,25 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302664</t>
+          <t xml:space="preserve">227307, 227308, 227309, 227310, 227311, 227312</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H93">
-        <v>1394</v>
+        <v>584</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311648515</t>
+          <t xml:space="preserve">311651635</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-12</t>
+          <t xml:space="preserve">2032-12-27</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydvestvej 10</t>
+          <t xml:space="preserve">Digevangsvej 1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119333</t>
+          <t xml:space="preserve">2121201</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5630,16 +5630,16 @@
         </is>
       </c>
       <c r="H94">
-        <v>4109</v>
+        <v>4686</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311648516</t>
+          <t xml:space="preserve">311653652</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-12</t>
+          <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 97</t>
+          <t xml:space="preserve">Digevangsvej 1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5681,25 +5681,25 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119766</t>
+          <t xml:space="preserve">2121201</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H95">
-        <v>254</v>
+        <v>3374</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651636</t>
+          <t xml:space="preserve">311653656</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-27</t>
+          <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 51</t>
+          <t xml:space="preserve">Asylvej 1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119885</t>
+          <t xml:space="preserve">228152, 228153</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5750,16 +5750,16 @@
         </is>
       </c>
       <c r="H96">
-        <v>418</v>
+        <v>1744</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651634</t>
+          <t xml:space="preserve">311662687</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-27</t>
+          <t xml:space="preserve">2033-02-27</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digevangsvej 1</t>
+          <t xml:space="preserve">Bøgeskoven 2</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5801,25 +5801,25 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121201</t>
+          <t xml:space="preserve">7942754</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H97">
-        <v>4686</v>
+        <v>596</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653652</t>
+          <t xml:space="preserve">311662692</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-12</t>
+          <t xml:space="preserve">2033-02-27</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digevangsvej 1</t>
+          <t xml:space="preserve">Bøgeskoven 4</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5861,25 +5861,25 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121201</t>
+          <t xml:space="preserve">7942754</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H98">
-        <v>3374</v>
+        <v>498</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653656</t>
+          <t xml:space="preserve">311662694</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-12</t>
+          <t xml:space="preserve">2033-02-27</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgeskoven 4</t>
+          <t xml:space="preserve">Stenager 2</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5981,20 +5981,20 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">7942754</t>
+          <t xml:space="preserve">9905315</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H100">
-        <v>498</v>
+        <v>7139</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311662694</t>
+          <t xml:space="preserve">311662695</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgeskoven 2</t>
+          <t xml:space="preserve">Solvangsvej 26A</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6041,25 +6041,25 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">7942754</t>
+          <t xml:space="preserve">712017, 2120435</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H101">
-        <v>596</v>
+        <v>254</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311662692</t>
+          <t xml:space="preserve">311683592</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-27</t>
+          <t xml:space="preserve">2033-05-26</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenager 2</t>
+          <t xml:space="preserve">Statenevej 46</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9905315</t>
+          <t xml:space="preserve">2117868</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6110,16 +6110,16 @@
         </is>
       </c>
       <c r="H102">
-        <v>7139</v>
+        <v>309</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311662695</t>
+          <t xml:space="preserve">311683595</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-27</t>
+          <t xml:space="preserve">2033-05-26</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statenevej 46</t>
+          <t xml:space="preserve">Vestergårdsvej 16A</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2117868</t>
+          <t xml:space="preserve">226855, 226856</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6170,16 +6170,16 @@
         </is>
       </c>
       <c r="H103">
-        <v>309</v>
+        <v>1125</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683595</t>
+          <t xml:space="preserve">311691228</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-26</t>
+          <t xml:space="preserve">2033-06-28</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solvangsvej 26A</t>
+          <t xml:space="preserve">Digevangsvej 5</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6221,25 +6221,25 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">712017, 2120435</t>
+          <t xml:space="preserve">2121201</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H104">
-        <v>254</v>
+        <v>1609</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683592</t>
+          <t xml:space="preserve">311739998</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-26</t>
+          <t xml:space="preserve">2034-02-20</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digevangsvej 5</t>
+          <t xml:space="preserve">Eriksvej 22</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6281,25 +6281,25 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121201</t>
+          <t xml:space="preserve">2119215</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H105">
-        <v>1609</v>
+        <v>1542</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739998</t>
+          <t xml:space="preserve">311751667</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-20</t>
+          <t xml:space="preserve">2034-04-12</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eriksvej 22</t>
+          <t xml:space="preserve">Hvissingevej 63B</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119215</t>
+          <t xml:space="preserve">100040949</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6350,16 +6350,16 @@
         </is>
       </c>
       <c r="H106">
-        <v>1542</v>
+        <v>431</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311751667</t>
+          <t xml:space="preserve">311794959</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-12</t>
+          <t xml:space="preserve">2034-11-01</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvissingevej 63B</t>
+          <t xml:space="preserve">Byparkvej 87</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">100040949</t>
+          <t xml:space="preserve">2121572</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6410,16 +6410,16 @@
         </is>
       </c>
       <c r="H107">
-        <v>431</v>
+        <v>4798</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311794959</t>
+          <t xml:space="preserve">311798616</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-01</t>
+          <t xml:space="preserve">2034-11-21</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byparkvej 87</t>
+          <t xml:space="preserve">Søndervangsvej 90</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6461,25 +6461,25 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121572</t>
+          <t xml:space="preserve">2120299</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H108">
-        <v>4798</v>
+        <v>858</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311798613</t>
+          <t xml:space="preserve">311869006</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-21</t>
+          <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndervangsvej 90</t>
+          <t xml:space="preserve">Rådhusparken 1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6521,25 +6521,25 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120299</t>
+          <t xml:space="preserve">229532, 229533, 229534</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H109">
-        <v>858</v>
+        <v>9132</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869006</t>
+          <t xml:space="preserve">311870463</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-18</t>
+          <t xml:space="preserve">2035-11-27</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">

--- a/public/exports/65120119.xlsx
+++ b/public/exports/65120119.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">

--- a/public/exports/65120119.xlsx
+++ b/public/exports/65120119.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588705</t>
+          <t xml:space="preserve">311588706</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588705</t>
+          <t xml:space="preserve">311588706</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588705</t>
+          <t xml:space="preserve">311588706</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588705</t>
+          <t xml:space="preserve">311588706</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588705</t>
+          <t xml:space="preserve">311588706</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588705</t>
+          <t xml:space="preserve">311588706</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588705</t>
+          <t xml:space="preserve">311588706</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588705</t>
+          <t xml:space="preserve">311588706</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588705</t>
+          <t xml:space="preserve">311588706</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588705</t>
+          <t xml:space="preserve">311588706</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588705</t>
+          <t xml:space="preserve">311588706</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588705</t>
+          <t xml:space="preserve">311588706</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590123</t>
+          <t xml:space="preserve">311590119</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590120</t>
+          <t xml:space="preserve">311590119</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590120</t>
+          <t xml:space="preserve">311590119</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311639469</t>
+          <t xml:space="preserve">311639468</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311639470</t>
+          <t xml:space="preserve">311639468</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311639471</t>
+          <t xml:space="preserve">311639468</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311640300</t>
+          <t xml:space="preserve">311640298</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311798616</t>
+          <t xml:space="preserve">311798613</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">

--- a/public/exports/65120119.xlsx
+++ b/public/exports/65120119.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:M109"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -299,15 +319,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t xml:space="preserve">dansk drift center ApS</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-03-03</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -359,15 +384,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t xml:space="preserve">dansk drift center ApS</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-17</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -419,15 +449,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t xml:space="preserve">dansk drift center ApS</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -479,15 +514,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-22</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -539,15 +579,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-02-07</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -599,15 +644,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Peter Knudsen, rådgivende ingeniørfirma FRI</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-15</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -659,15 +709,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-05-25</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -719,15 +774,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Energi- og Byggerådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-12-23</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -779,15 +839,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-16</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -839,15 +904,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-07</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -894,20 +964,25 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -954,20 +1029,25 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1014,20 +1094,25 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1074,20 +1159,25 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1134,20 +1224,25 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1194,20 +1289,25 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1254,20 +1354,25 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1314,20 +1419,25 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1374,20 +1484,25 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1434,20 +1549,25 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1494,20 +1614,25 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1554,20 +1679,25 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588706</t>
+          <t xml:space="preserve">311588705</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2154,20 +2329,25 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590119</t>
+          <t xml:space="preserve">311590114</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2214,20 +2394,25 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590111</t>
+          <t xml:space="preserve">311590114</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2274,20 +2459,25 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590119</t>
+          <t xml:space="preserve">311590114</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2334,20 +2524,25 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590119</t>
+          <t xml:space="preserve">311590114</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-01</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-04</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-27</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-27</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-01</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-01</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-01</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-01</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-03</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-03</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-03</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-03</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-12</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-12</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-12</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-12</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-27</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-27</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-27</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-27</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-27</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-27</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-27</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-27</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-26</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-26</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-28</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-20</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">ISOLINK ApS</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-04-12</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-01</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6414,20 +6944,25 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311798613</t>
+          <t xml:space="preserve">311798611</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-21</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,21 +7079,26 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-27</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L109"/>
+  <autoFilter ref="A1:M109"/>
 </worksheet>
 </file>
--- a/public/exports/65120119.xlsx
+++ b/public/exports/65120119.xlsx
@@ -2394,7 +2394,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590114</t>
+          <t xml:space="preserve">311590111</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
